--- a/Testdata.xlsx
+++ b/Testdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubRepo\finresolver\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubRepo\finresolver\finresolver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8F1F5A-1204-4C1D-BDF7-A2BDC917932C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7AC933-6A57-4FE5-AA45-B3876FAC33E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4D685F45-FFFE-433C-A801-F3E9437C90C4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>Current Balance</t>
   </si>
@@ -105,9 +105,6 @@
     <t>School Sports Fee</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>From Appa</t>
   </si>
   <si>
@@ -135,49 +132,19 @@
     <t>Donation amount</t>
   </si>
   <si>
-    <t>MF Redeption</t>
-  </si>
-  <si>
-    <t>Cricket</t>
-  </si>
-  <si>
-    <t>To IDFC</t>
-  </si>
-  <si>
-    <t>From Vinoth</t>
-  </si>
-  <si>
-    <t>Div - TCS</t>
-  </si>
-  <si>
-    <t>From Diwakar</t>
-  </si>
-  <si>
-    <t>Div - Styrenix</t>
-  </si>
-  <si>
-    <t>Div - PGInvit</t>
-  </si>
-  <si>
-    <t>Regular Expense</t>
-  </si>
-  <si>
-    <t>Div - Gulf Oil</t>
-  </si>
-  <si>
-    <t>Travel</t>
-  </si>
-  <si>
-    <t>Lic</t>
-  </si>
-  <si>
-    <t>Div - Natco</t>
-  </si>
-  <si>
-    <t>Div - ITC</t>
-  </si>
-  <si>
-    <t>Div - Power Grid</t>
+    <t>IDFC CC</t>
+  </si>
+  <si>
+    <t>SC CC</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Amex CC</t>
+  </si>
+  <si>
+    <t>Regular Expenses</t>
   </si>
 </sst>
 </file>
@@ -624,26 +591,26 @@
   <sheetData>
     <row r="1" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2">
         <v>9602.68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="2">
-        <v>1780.48</v>
-      </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+        <v>47740.68</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -660,11 +627,11 @@
         <v>6</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="I2" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -689,8 +656,8 @@
       <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>10</v>
+      <c r="I3" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -704,7 +671,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="2">
-        <v>243396</v>
+        <v>244515</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>13</v>
@@ -719,7 +686,7 @@
         <v>30000</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -730,13 +697,11 @@
         <v>20000</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2">
-        <v>10000</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2">
         <v>15000</v>
@@ -748,22 +713,20 @@
         <v>58877</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="2">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="2">
-        <v>310</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
@@ -773,212 +736,142 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2">
-        <v>25000</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1767</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="4" t="s">
-        <v>25</v>
+      <c r="I7" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2">
-        <v>500</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="2">
-        <v>33200</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2">
-        <v>4000</v>
+        <v>25000</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="2">
-        <v>30111</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="2">
-        <v>150</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F9" s="2">
-        <v>25000</v>
+        <v>2000</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="4" t="s">
-        <v>29</v>
+      <c r="I9" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2">
-        <v>3500</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="2">
-        <v>299</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2000</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="4" t="s">
-        <v>30</v>
+      <c r="I10" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2">
-        <v>231.8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2">
-        <v>926</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="2">
-        <v>10000</v>
-      </c>
+        <v>11322</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="2">
-        <v>8000</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="2">
-        <v>250</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="2">
-        <v>10000</v>
-      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="2"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="2">
-        <v>11998</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2">
-        <v>7500</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3500</v>
-      </c>
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="2"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="2">
-        <v>491</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="2">
-        <v>18000</v>
-      </c>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2">
-        <v>40</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="2">
-        <v>172.5</v>
-      </c>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -988,27 +881,19 @@
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1853</v>
-      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="2"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="2">
-        <v>747.5</v>
-      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
